--- a/files/第16届蓝桥杯大赛报名和获奖情况统计表.xlsx
+++ b/files/第16届蓝桥杯大赛报名和获奖情况统计表.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="2820" windowHeight="4540"/>
   </bookViews>
   <sheets>
-    <sheet name="2025年报名和获奖情况" sheetId="1" r:id="rId1"/>
+    <sheet name="第16届报名和获奖情况" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -319,6 +319,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1745,35 +1746,35 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1">
-        <f>SUM(C30:C37)</f>
+        <f t="shared" ref="C38:J38" si="5">SUM(C30:C37)</f>
         <v>541</v>
       </c>
       <c r="D38" s="1">
-        <f>SUM(D30:D37)</f>
+        <f t="shared" si="5"/>
         <v>93</v>
       </c>
       <c r="E38" s="1">
-        <f>SUM(E30:E37)</f>
+        <f t="shared" si="5"/>
         <v>189</v>
       </c>
       <c r="F38" s="1">
-        <f>SUM(F30:F37)</f>
+        <f t="shared" si="5"/>
         <v>259</v>
       </c>
       <c r="G38" s="1">
-        <f>SUM(G30:G37)</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="H38" s="1">
-        <f>SUM(H30:H37)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="I38" s="1">
-        <f>SUM(I30:I37)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="J38" s="1">
-        <f>SUM(J30:J37)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -1828,7 +1829,7 @@
         <v>22</v>
       </c>
       <c r="C41" s="1">
-        <f>SUM(D41:F41)</f>
+        <f t="shared" ref="C41:C46" si="6">SUM(D41:F41)</f>
         <v>58</v>
       </c>
       <c r="D41" s="1">
@@ -1841,7 +1842,7 @@
         <v>15</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" ref="G41:G46" si="5">SUM(H41:J41)</f>
+        <f t="shared" ref="G41:G46" si="7">SUM(H41:J41)</f>
         <v>16</v>
       </c>
       <c r="H41" s="2">
@@ -1862,7 +1863,7 @@
         <v>22</v>
       </c>
       <c r="C42" s="1">
-        <f>SUM(D42:F42)</f>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="D42" s="1">
@@ -1875,7 +1876,7 @@
         <v>12</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H42" s="2">
@@ -1896,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="C43" s="1">
-        <f>SUM(D43:F43)</f>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="D43" s="1">
@@ -1909,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="G43" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="H43" s="2">
@@ -1930,7 +1931,7 @@
         <v>22</v>
       </c>
       <c r="C44" s="1">
-        <f>SUM(D44:F44)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D44" s="1">
@@ -1943,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H44" s="2">
@@ -1964,7 +1965,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="1">
-        <f>SUM(D45:F45)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D45" s="1">
@@ -1977,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <f t="shared" ref="G45" si="6">SUM(H45:J45)</f>
+        <f t="shared" ref="G45" si="8">SUM(H45:J45)</f>
         <v>0</v>
       </c>
       <c r="H45" s="2">
@@ -1998,7 +1999,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="1">
-        <f>SUM(D46:F46)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D46" s="1">
@@ -2011,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H46" s="2">
@@ -2030,35 +2031,35 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1">
-        <f>SUM(C41:C46)</f>
+        <f t="shared" ref="C47:J47" si="9">SUM(C41:C46)</f>
         <v>117</v>
       </c>
       <c r="D47" s="1">
-        <f>SUM(D41:D46)</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="E47" s="1">
-        <f>SUM(E41:E46)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="F47" s="1">
-        <f>SUM(F41:F46)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="G47" s="1">
-        <f>SUM(G41:G46)</f>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="H47" s="1">
-        <f>SUM(H41:H46)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="I47" s="1">
-        <f>SUM(I41:I46)</f>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="J47" s="1">
-        <f>SUM(J41:J46)</f>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
@@ -2136,35 +2137,35 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <f t="shared" ref="C51" si="7">C50</f>
+        <f t="shared" ref="C51" si="10">C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" ref="D51" si="8">D50</f>
+        <f t="shared" ref="D51" si="11">D50</f>
         <v>1</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" ref="E51" si="9">E50</f>
+        <f t="shared" ref="E51" si="12">E50</f>
         <v>1</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" ref="F51" si="10">F50</f>
+        <f t="shared" ref="F51" si="13">F50</f>
         <v>2</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" ref="G51" si="11">G50</f>
+        <f t="shared" ref="G51" si="14">G50</f>
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" ref="H51" si="12">H50</f>
+        <f t="shared" ref="H51" si="15">H50</f>
         <v>0</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" ref="I51" si="13">I50</f>
+        <f t="shared" ref="I51" si="16">I50</f>
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" ref="J51" si="14">J50</f>
+        <f t="shared" ref="J51" si="17">J50</f>
         <v>0</v>
       </c>
     </row>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1">
-        <f t="shared" ref="C57:C65" si="15">SUM(D57:F57)</f>
+        <f t="shared" ref="C57:C65" si="18">SUM(D57:F57)</f>
         <v>1</v>
       </c>
       <c r="D57" s="1">
@@ -2325,7 +2326,7 @@
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D58" s="1">
@@ -2357,7 +2358,7 @@
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D59" s="1">
@@ -2389,7 +2390,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
       <c r="D60" s="1">
@@ -2412,7 +2413,7 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D61" s="1">
@@ -2444,7 +2445,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D62" s="1">
@@ -2476,7 +2477,7 @@
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="D63" s="1">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D64" s="1">
@@ -2542,7 +2543,7 @@
         <v>59</v>
       </c>
       <c r="C65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D65" s="1">
@@ -2555,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <f t="shared" ref="G65" si="16">SUM(H65:J65)</f>
+        <f t="shared" ref="G65" si="19">SUM(H65:J65)</f>
         <v>0</v>
       </c>
       <c r="H65" s="1">
@@ -2602,7 +2603,7 @@
         <v>63</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" ref="G67:G69" si="17">SUM(H67:J67)</f>
+        <f t="shared" ref="G67:G69" si="20">SUM(H67:J67)</f>
         <v>1</v>
       </c>
       <c r="H67" s="2">
@@ -2633,7 +2634,7 @@
         <v>63</v>
       </c>
       <c r="G68" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="H68" s="2">
@@ -2652,7 +2653,7 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1">
-        <f t="shared" ref="C69" si="18">SUM(D69:F69)</f>
+        <f t="shared" ref="C69" si="21">SUM(D69:F69)</f>
         <v>0</v>
       </c>
       <c r="D69" s="1">
@@ -2665,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H69" s="2">
@@ -2688,31 +2689,31 @@
         <v>26</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" ref="D70:J70" si="19">SUM(D54:D69)</f>
+        <f t="shared" ref="D70:J70" si="22">SUM(D54:D69)</f>
         <v>4</v>
       </c>
       <c r="E70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="F70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
     </row>
